--- a/data/aa2_1_h.xlsx
+++ b/data/aa2_1_h.xlsx
@@ -5,14 +5,14 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GinrutPrices\Output\A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\odelyas\Desktop\AA\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7815" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="AA.2.1 1994-2010" sheetId="2" r:id="rId1"/>
+    <sheet name="AA.2.1 1994-2010" sheetId="3" r:id="rId1"/>
     <sheet name="AA.2.1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
@@ -20,9 +20,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="794">
-  <si>
-    <t>הופק לאחרונה עבור ירחון מחירים מס' 4/2026, הלשכה המרכזית לסטטיסטיקה</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="800">
+  <si>
+    <t>הופק לאחרונה עבור ירחון מחירים מס' 7/2026, הלשכה המרכזית לסטטיסטיקה</t>
   </si>
   <si>
     <t>הבסיס: ממוצע 1993=100.0</t>
@@ -1205,6 +1205,24 @@
   </si>
   <si>
     <t>15/05/2026</t>
+  </si>
+  <si>
+    <t>מרס 2026 - אפריל 2026</t>
+  </si>
+  <si>
+    <t>15/06/2026</t>
+  </si>
+  <si>
+    <t>אפריל 2026 - מאי 2026</t>
+  </si>
+  <si>
+    <t>15/07/2026</t>
+  </si>
+  <si>
+    <t>מאי 2026 - יוני 2026</t>
+  </si>
+  <si>
+    <t>15/08/2026</t>
   </si>
   <si>
     <t>(1) החל בינואר 1999 מדד זה משמש כאינדיקטור לשינויים במחירי דירות</t>
@@ -1259,1156 +1277,1156 @@
     </r>
   </si>
   <si>
+    <t>15/04/1994</t>
+  </si>
+  <si>
+    <t>15/05/1994</t>
+  </si>
+  <si>
+    <t>15/06/1994</t>
+  </si>
+  <si>
+    <t>15/07/1994</t>
+  </si>
+  <si>
+    <t>15/08/1994</t>
+  </si>
+  <si>
+    <t>15/09/1994</t>
+  </si>
+  <si>
+    <t>15/10/1994</t>
+  </si>
+  <si>
+    <t>15/11/1994</t>
+  </si>
+  <si>
+    <t>15/12/1994</t>
+  </si>
+  <si>
+    <t>15/01/1995</t>
+  </si>
+  <si>
+    <t>15/02/1995</t>
+  </si>
+  <si>
+    <t>15/03/1995</t>
+  </si>
+  <si>
+    <t>15/04/1995</t>
+  </si>
+  <si>
+    <t>15/05/1995</t>
+  </si>
+  <si>
+    <t>15/06/1995</t>
+  </si>
+  <si>
+    <t>15/07/1995</t>
+  </si>
+  <si>
+    <t>15/08/1995</t>
+  </si>
+  <si>
+    <t>15/09/1995</t>
+  </si>
+  <si>
+    <t>15/10/1995</t>
+  </si>
+  <si>
+    <t>15/11/1995</t>
+  </si>
+  <si>
+    <t>15/12/1995</t>
+  </si>
+  <si>
+    <t>15/01/1996</t>
+  </si>
+  <si>
+    <t>15/02/1996</t>
+  </si>
+  <si>
+    <t>15/03/1996</t>
+  </si>
+  <si>
+    <t>15/04/1996</t>
+  </si>
+  <si>
+    <t>15/05/1996</t>
+  </si>
+  <si>
+    <t>15/06/1996</t>
+  </si>
+  <si>
+    <t>15/07/1996</t>
+  </si>
+  <si>
+    <t>15/08/1996</t>
+  </si>
+  <si>
+    <t>15/09/1996</t>
+  </si>
+  <si>
+    <t>15/10/1996</t>
+  </si>
+  <si>
+    <t>15/11/1996</t>
+  </si>
+  <si>
+    <t>15/12/1996</t>
+  </si>
+  <si>
+    <t>15/01/1997</t>
+  </si>
+  <si>
+    <t>15/02/1997</t>
+  </si>
+  <si>
+    <t>15/03/1997</t>
+  </si>
+  <si>
+    <t>15/04/1997</t>
+  </si>
+  <si>
+    <t>15/05/1997</t>
+  </si>
+  <si>
+    <t>15/06/1997</t>
+  </si>
+  <si>
+    <t>15/07/1997</t>
+  </si>
+  <si>
+    <t>15/08/1997</t>
+  </si>
+  <si>
+    <t>15/09/1997</t>
+  </si>
+  <si>
+    <t>15/10/1997</t>
+  </si>
+  <si>
+    <t>15/11/1997</t>
+  </si>
+  <si>
+    <t>15/12/1997</t>
+  </si>
+  <si>
+    <t>15/01/1998</t>
+  </si>
+  <si>
+    <t>15/02/1998</t>
+  </si>
+  <si>
+    <t>15/03/1998</t>
+  </si>
+  <si>
+    <t>15/04/1998</t>
+  </si>
+  <si>
+    <t>15/05/1998</t>
+  </si>
+  <si>
+    <t>15/06/1998</t>
+  </si>
+  <si>
+    <t>15/07/1998</t>
+  </si>
+  <si>
+    <t>15/08/1998</t>
+  </si>
+  <si>
+    <t>15/09/1998</t>
+  </si>
+  <si>
+    <t>15/10/1998</t>
+  </si>
+  <si>
+    <t>15/11/1998</t>
+  </si>
+  <si>
+    <t>15/12/1998</t>
+  </si>
+  <si>
+    <t>15/01/1999</t>
+  </si>
+  <si>
+    <t>15/02/1999</t>
+  </si>
+  <si>
+    <t>15/03/1999</t>
+  </si>
+  <si>
+    <t>15/04/1999</t>
+  </si>
+  <si>
+    <t>15/05/1999</t>
+  </si>
+  <si>
+    <t>15/06/1999</t>
+  </si>
+  <si>
+    <t>15/07/1999</t>
+  </si>
+  <si>
+    <t>15/08/1999</t>
+  </si>
+  <si>
+    <t>15/09/1999</t>
+  </si>
+  <si>
+    <t>15/10/1999</t>
+  </si>
+  <si>
+    <t>15/11/1999</t>
+  </si>
+  <si>
+    <t>15/12/1999</t>
+  </si>
+  <si>
+    <t>15/01/2000</t>
+  </si>
+  <si>
+    <t>15/02/2000</t>
+  </si>
+  <si>
+    <t>15/03/2000</t>
+  </si>
+  <si>
+    <t>15/04/2000</t>
+  </si>
+  <si>
+    <t>15/05/2000</t>
+  </si>
+  <si>
+    <t>15/06/2000</t>
+  </si>
+  <si>
+    <t>15/07/2000</t>
+  </si>
+  <si>
+    <t>15/08/2000</t>
+  </si>
+  <si>
+    <t>15/09/2000</t>
+  </si>
+  <si>
+    <t>15/10/2000</t>
+  </si>
+  <si>
+    <t>15/11/2000</t>
+  </si>
+  <si>
+    <t>15/12/2000</t>
+  </si>
+  <si>
+    <t>15/01/2001</t>
+  </si>
+  <si>
+    <t>15/02/2001</t>
+  </si>
+  <si>
+    <t>15/03/2001</t>
+  </si>
+  <si>
+    <t>15/04/2001</t>
+  </si>
+  <si>
+    <t>15/05/2001</t>
+  </si>
+  <si>
+    <t>15/06/2001</t>
+  </si>
+  <si>
+    <t>15/07/2001</t>
+  </si>
+  <si>
+    <t>15/08/2001</t>
+  </si>
+  <si>
+    <t>15/09/2001</t>
+  </si>
+  <si>
+    <t>15/10/2001</t>
+  </si>
+  <si>
+    <t>15/11/2001</t>
+  </si>
+  <si>
+    <t>15/12/2001</t>
+  </si>
+  <si>
+    <t>15/01/2002</t>
+  </si>
+  <si>
+    <t>15/02/2002</t>
+  </si>
+  <si>
+    <t>15/03/2002</t>
+  </si>
+  <si>
+    <t>15/04/2002</t>
+  </si>
+  <si>
+    <t>15/05/2002</t>
+  </si>
+  <si>
+    <t>15/06/2002</t>
+  </si>
+  <si>
+    <t>15/07/2002</t>
+  </si>
+  <si>
+    <t>15/08/2002</t>
+  </si>
+  <si>
+    <t>15/09/2002</t>
+  </si>
+  <si>
+    <t>15/10/2002</t>
+  </si>
+  <si>
+    <t>15/11/2002</t>
+  </si>
+  <si>
+    <t>15/12/2002</t>
+  </si>
+  <si>
+    <t>15/01/2003</t>
+  </si>
+  <si>
+    <t>15/02/2003</t>
+  </si>
+  <si>
+    <t>15/03/2003</t>
+  </si>
+  <si>
+    <t>15/04/2003</t>
+  </si>
+  <si>
+    <t>15/05/2003</t>
+  </si>
+  <si>
+    <t>15/06/2003</t>
+  </si>
+  <si>
+    <t>15/07/2003</t>
+  </si>
+  <si>
+    <t>15/08/2003</t>
+  </si>
+  <si>
+    <t>15/09/2003</t>
+  </si>
+  <si>
+    <t>15/10/2003</t>
+  </si>
+  <si>
+    <t>15/11/2003</t>
+  </si>
+  <si>
+    <t>15/12/2003</t>
+  </si>
+  <si>
+    <t>15/01/2004</t>
+  </si>
+  <si>
+    <t>15/02/2004</t>
+  </si>
+  <si>
+    <t>15/03/2004</t>
+  </si>
+  <si>
+    <t>15/04/2004</t>
+  </si>
+  <si>
+    <t>15/05/2004</t>
+  </si>
+  <si>
+    <t>15/06/2004</t>
+  </si>
+  <si>
+    <t>15/07/2004</t>
+  </si>
+  <si>
+    <t>15/08/2004</t>
+  </si>
+  <si>
+    <t>15/09/2004</t>
+  </si>
+  <si>
+    <t>15/10/2004</t>
+  </si>
+  <si>
+    <t>15/11/2004</t>
+  </si>
+  <si>
+    <t>15/12/2004</t>
+  </si>
+  <si>
+    <t>15/01/2005</t>
+  </si>
+  <si>
+    <t>15/02/2005</t>
+  </si>
+  <si>
+    <t>15/03/2005</t>
+  </si>
+  <si>
+    <t>15/04/2005</t>
+  </si>
+  <si>
+    <t>15/05/2005</t>
+  </si>
+  <si>
+    <t>15/06/2005</t>
+  </si>
+  <si>
+    <t>15/07/2005</t>
+  </si>
+  <si>
+    <t>15/08/2005</t>
+  </si>
+  <si>
+    <t>15/09/2005</t>
+  </si>
+  <si>
+    <t>15/10/2005</t>
+  </si>
+  <si>
+    <t>15/11/2005</t>
+  </si>
+  <si>
+    <t>15/12/2005</t>
+  </si>
+  <si>
+    <t>15/01/2006</t>
+  </si>
+  <si>
+    <t>15/02/2006</t>
+  </si>
+  <si>
+    <t>15/03/2006</t>
+  </si>
+  <si>
+    <t>15/04/2006</t>
+  </si>
+  <si>
+    <t>15/05/2006</t>
+  </si>
+  <si>
+    <t>15/06/2006</t>
+  </si>
+  <si>
+    <t>15/07/2006</t>
+  </si>
+  <si>
+    <t>15/08/2006</t>
+  </si>
+  <si>
+    <t>15/09/2006</t>
+  </si>
+  <si>
+    <t>15/10/2006</t>
+  </si>
+  <si>
+    <t>15/11/2006</t>
+  </si>
+  <si>
+    <t>15/12/2006</t>
+  </si>
+  <si>
+    <t>15/01/2007</t>
+  </si>
+  <si>
+    <t>15/02/2007</t>
+  </si>
+  <si>
+    <t>15/03/2007</t>
+  </si>
+  <si>
+    <t>15/04/2007</t>
+  </si>
+  <si>
+    <t>15/05/2007</t>
+  </si>
+  <si>
+    <t>15/06/2007</t>
+  </si>
+  <si>
+    <t>15/07/2007</t>
+  </si>
+  <si>
+    <t>15/08/2007</t>
+  </si>
+  <si>
+    <t>15/09/2007</t>
+  </si>
+  <si>
+    <t>15/10/2007</t>
+  </si>
+  <si>
+    <t>15/11/2007</t>
+  </si>
+  <si>
+    <t>15/12/2007</t>
+  </si>
+  <si>
+    <t>15/01/2008</t>
+  </si>
+  <si>
+    <t>15/02/2008</t>
+  </si>
+  <si>
+    <t>15/03/2008</t>
+  </si>
+  <si>
+    <t>15/04/2008</t>
+  </si>
+  <si>
+    <t>15/05/2008</t>
+  </si>
+  <si>
+    <t>15/06/2008</t>
+  </si>
+  <si>
+    <t>15/07/2008</t>
+  </si>
+  <si>
+    <t>15/08/2008</t>
+  </si>
+  <si>
+    <t>15/09/2008</t>
+  </si>
+  <si>
+    <t>15/10/2008</t>
+  </si>
+  <si>
+    <t>15/11/2008</t>
+  </si>
+  <si>
+    <t>15/12/2008</t>
+  </si>
+  <si>
+    <t>15/01/2009</t>
+  </si>
+  <si>
+    <t>15/02/2009</t>
+  </si>
+  <si>
+    <t>15/03/2009</t>
+  </si>
+  <si>
+    <t>15/04/2009</t>
+  </si>
+  <si>
+    <t>15/05/2009</t>
+  </si>
+  <si>
+    <t>15/06/2009</t>
+  </si>
+  <si>
+    <t>15/07/2009</t>
+  </si>
+  <si>
+    <t>15/08/2009</t>
+  </si>
+  <si>
+    <t>15/09/2009</t>
+  </si>
+  <si>
+    <t>15/10/2009</t>
+  </si>
+  <si>
+    <t>15/11/2009</t>
+  </si>
+  <si>
+    <t>15/12/2009</t>
+  </si>
+  <si>
+    <t>15/01/2010</t>
+  </si>
+  <si>
+    <t>15/02/2010</t>
+  </si>
+  <si>
+    <t>15/03/2010</t>
+  </si>
+  <si>
     <t>הופק לאחרונה עבור ירחון מחירים מס' 5/2022, הלשכה המרכזית לסטטיסטיקה</t>
   </si>
   <si>
-    <t>15/04/1994</t>
-  </si>
-  <si>
     <t>ינואר 1994 - פברואר 1994</t>
   </si>
   <si>
-    <t>15/05/1994</t>
-  </si>
-  <si>
     <t>פברואר 1994 - מרס 1994</t>
   </si>
   <si>
-    <t>15/06/1994</t>
-  </si>
-  <si>
     <t>מרס 1994 - אפריל 1994</t>
   </si>
   <si>
-    <t>15/07/1994</t>
-  </si>
-  <si>
     <t>אפריל 1994 - מאי 1994</t>
   </si>
   <si>
-    <t>15/08/1994</t>
-  </si>
-  <si>
     <t>מאי 1994 - יוני 1994</t>
   </si>
   <si>
-    <t>15/09/1994</t>
-  </si>
-  <si>
     <t>יוני 1994 - יולי 1994</t>
   </si>
   <si>
-    <t>15/10/1994</t>
-  </si>
-  <si>
     <t>יולי 1994 - אוגוסט 1994</t>
   </si>
   <si>
-    <t>15/11/1994</t>
-  </si>
-  <si>
     <t>אוגוסט 1994 - ספטמבר 1994</t>
   </si>
   <si>
-    <t>15/12/1994</t>
-  </si>
-  <si>
     <t>ספטמבר 1994 - אוקטובר 1994</t>
   </si>
   <si>
-    <t>15/01/1995</t>
-  </si>
-  <si>
     <t>אוקטובר 1994 - נובמבר 1994</t>
   </si>
   <si>
-    <t>15/02/1995</t>
-  </si>
-  <si>
     <t>נובמבר 1994 - דצמבר 1994</t>
   </si>
   <si>
-    <t>15/03/1995</t>
-  </si>
-  <si>
     <t>דצמבר 1994 - ינואר 1995</t>
   </si>
   <si>
-    <t>15/04/1995</t>
-  </si>
-  <si>
     <t>ינואר 1995 - פברואר 1995</t>
   </si>
   <si>
-    <t>15/05/1995</t>
-  </si>
-  <si>
     <t>פברואר 1995 - מרס 1995</t>
   </si>
   <si>
-    <t>15/06/1995</t>
-  </si>
-  <si>
     <t>מרס 1995 - אפריל 1995</t>
   </si>
   <si>
-    <t>15/07/1995</t>
-  </si>
-  <si>
     <t>אפריל 1995 - מאי 1995</t>
   </si>
   <si>
-    <t>15/08/1995</t>
-  </si>
-  <si>
     <t>מאי 1995 - יוני 1995</t>
   </si>
   <si>
-    <t>15/09/1995</t>
-  </si>
-  <si>
     <t>יוני 1995 - יולי 1995</t>
   </si>
   <si>
-    <t>15/10/1995</t>
-  </si>
-  <si>
     <t>יולי 1995 - אוגוסט 1995</t>
   </si>
   <si>
-    <t>15/11/1995</t>
-  </si>
-  <si>
     <t>אוגוסט 1995 - ספטמבר 1995</t>
   </si>
   <si>
-    <t>15/12/1995</t>
-  </si>
-  <si>
     <t>ספטמבר 1995 - אוקטובר 1995</t>
   </si>
   <si>
-    <t>15/01/1996</t>
-  </si>
-  <si>
     <t>אוקטובר 1995 - נובמבר 1995</t>
   </si>
   <si>
-    <t>15/02/1996</t>
-  </si>
-  <si>
     <t>נובמבר 1995 - דצמבר 1995</t>
   </si>
   <si>
-    <t>15/03/1996</t>
-  </si>
-  <si>
     <t>דצמבר 1995 - ינואר 1996</t>
   </si>
   <si>
-    <t>15/04/1996</t>
-  </si>
-  <si>
     <t>ינואר 1996 - פברואר 1996</t>
   </si>
   <si>
-    <t>15/05/1996</t>
-  </si>
-  <si>
     <t>פברואר 1996 - מרס 1996</t>
   </si>
   <si>
-    <t>15/06/1996</t>
-  </si>
-  <si>
     <t>מרס 1996 - אפריל 1996</t>
   </si>
   <si>
-    <t>15/07/1996</t>
-  </si>
-  <si>
     <t>אפריל 1996 - מאי 1996</t>
   </si>
   <si>
-    <t>15/08/1996</t>
-  </si>
-  <si>
     <t>מאי 1996 - יוני 1996</t>
   </si>
   <si>
-    <t>15/09/1996</t>
-  </si>
-  <si>
     <t>יוני 1996 - יולי 1996</t>
   </si>
   <si>
-    <t>15/10/1996</t>
-  </si>
-  <si>
     <t>יולי 1996 - אוגוסט 1996</t>
   </si>
   <si>
-    <t>15/11/1996</t>
-  </si>
-  <si>
     <t>אוגוסט 1996 - ספטמבר 1996</t>
   </si>
   <si>
-    <t>15/12/1996</t>
-  </si>
-  <si>
     <t>ספטמבר 1996 - אוקטובר 1996</t>
   </si>
   <si>
-    <t>15/01/1997</t>
-  </si>
-  <si>
     <t>אוקטובר 1996 - נובמבר 1996</t>
   </si>
   <si>
-    <t>15/02/1997</t>
-  </si>
-  <si>
     <t>נובמבר 1996 - דצמבר 1996</t>
   </si>
   <si>
-    <t>15/03/1997</t>
-  </si>
-  <si>
     <t>דצמבר 1996 - ינואר 1997</t>
   </si>
   <si>
-    <t>15/04/1997</t>
-  </si>
-  <si>
     <t>ינואר 1997 - פברואר 1997</t>
   </si>
   <si>
-    <t>15/05/1997</t>
-  </si>
-  <si>
     <t>פברואר 1997 - מרס 1997</t>
   </si>
   <si>
-    <t>15/06/1997</t>
-  </si>
-  <si>
     <t>מרס 1997 - אפריל 1997</t>
   </si>
   <si>
-    <t>15/07/1997</t>
-  </si>
-  <si>
     <t>אפריל 1997 - מאי 1997</t>
   </si>
   <si>
-    <t>15/08/1997</t>
-  </si>
-  <si>
     <t>מאי 1997 - יוני 1997</t>
   </si>
   <si>
-    <t>15/09/1997</t>
-  </si>
-  <si>
     <t>יוני 1997 - יולי 1997</t>
   </si>
   <si>
-    <t>15/10/1997</t>
-  </si>
-  <si>
     <t>יולי 1997 - אוגוסט 1997</t>
   </si>
   <si>
-    <t>15/11/1997</t>
-  </si>
-  <si>
     <t>אוגוסט 1997 - ספטמבר 1997</t>
   </si>
   <si>
-    <t>15/12/1997</t>
-  </si>
-  <si>
     <t>ספטמבר 1997 - אוקטובר 1997</t>
   </si>
   <si>
-    <t>15/01/1998</t>
-  </si>
-  <si>
     <t>אוקטובר 1997 - נובמבר 1997</t>
   </si>
   <si>
-    <t>15/02/1998</t>
-  </si>
-  <si>
     <t>נובמבר 1997 - דצמבר 1997</t>
   </si>
   <si>
-    <t>15/03/1998</t>
-  </si>
-  <si>
     <t>דצמבר 1997 - ינואר 1998</t>
   </si>
   <si>
-    <t>15/04/1998</t>
-  </si>
-  <si>
     <t>ינואר 1998 - פברואר 1998</t>
   </si>
   <si>
-    <t>15/05/1998</t>
-  </si>
-  <si>
     <t>פברואר 1998 - מרס 1998</t>
   </si>
   <si>
-    <t>15/06/1998</t>
-  </si>
-  <si>
     <t>מרס 1998 - אפריל 1998</t>
   </si>
   <si>
-    <t>15/07/1998</t>
-  </si>
-  <si>
     <t>אפריל 1998 - מאי 1998</t>
   </si>
   <si>
-    <t>15/08/1998</t>
-  </si>
-  <si>
     <t>מאי 1998 - יוני 1998</t>
   </si>
   <si>
-    <t>15/09/1998</t>
-  </si>
-  <si>
     <t>יוני 1998 - יולי 1998</t>
   </si>
   <si>
-    <t>15/10/1998</t>
-  </si>
-  <si>
     <t>יולי 1998 - אוגוסט 1998</t>
   </si>
   <si>
-    <t>15/11/1998</t>
-  </si>
-  <si>
     <t>אוגוסט 1998 - ספטמבר 1998</t>
   </si>
   <si>
-    <t>15/12/1998</t>
-  </si>
-  <si>
     <t>ספטמבר 1998 - אוקטובר 1998</t>
   </si>
   <si>
-    <t>15/01/1999</t>
-  </si>
-  <si>
     <t>אוקטובר 1998 - נובמבר 1998</t>
   </si>
   <si>
-    <t>15/02/1999</t>
-  </si>
-  <si>
     <t>נובמבר 1998 - דצמבר 1998</t>
   </si>
   <si>
-    <t>15/03/1999</t>
-  </si>
-  <si>
     <t>דצמבר 1998 - ינואר 1999</t>
   </si>
   <si>
-    <t>15/04/1999</t>
-  </si>
-  <si>
     <t>ינואר 1999 - פברואר 1999</t>
   </si>
   <si>
-    <t>15/05/1999</t>
-  </si>
-  <si>
     <t>פברואר 1999 - מרס 1999</t>
   </si>
   <si>
-    <t>15/06/1999</t>
-  </si>
-  <si>
     <t>מרס 1999 - אפריל 1999</t>
   </si>
   <si>
-    <t>15/07/1999</t>
-  </si>
-  <si>
     <t>אפריל 1999 - מאי 1999</t>
   </si>
   <si>
-    <t>15/08/1999</t>
-  </si>
-  <si>
     <t>מאי 1999 - יוני 1999</t>
   </si>
   <si>
-    <t>15/09/1999</t>
-  </si>
-  <si>
     <t>יוני 1999 - יולי 1999</t>
   </si>
   <si>
-    <t>15/10/1999</t>
-  </si>
-  <si>
     <t>יולי 1999 - אוגוסט 1999</t>
   </si>
   <si>
-    <t>15/11/1999</t>
-  </si>
-  <si>
     <t>אוגוסט 1999 - ספטמבר 1999</t>
   </si>
   <si>
-    <t>15/12/1999</t>
-  </si>
-  <si>
     <t>ספטמבר 1999 - אוקטובר 1999</t>
   </si>
   <si>
-    <t>15/01/2000</t>
-  </si>
-  <si>
     <t>אוקטובר 1999 - נובמבר 1999</t>
   </si>
   <si>
-    <t>15/02/2000</t>
-  </si>
-  <si>
     <t>נובמבר 1999 - דצמבר 1999</t>
   </si>
   <si>
-    <t>15/03/2000</t>
-  </si>
-  <si>
     <t>דצמבר 1999 - ינואר 2000</t>
   </si>
   <si>
-    <t>15/04/2000</t>
-  </si>
-  <si>
     <t>ינואר 2000 - פברואר 2000</t>
   </si>
   <si>
-    <t>15/05/2000</t>
-  </si>
-  <si>
     <t>פברואר 2000 - מרס 2000</t>
   </si>
   <si>
-    <t>15/06/2000</t>
-  </si>
-  <si>
     <t>מרס 2000 - אפריל 2000</t>
   </si>
   <si>
-    <t>15/07/2000</t>
-  </si>
-  <si>
     <t>אפריל 2000 - מאי 2000</t>
   </si>
   <si>
-    <t>15/08/2000</t>
-  </si>
-  <si>
     <t>מאי 2000 - יוני 2000</t>
   </si>
   <si>
-    <t>15/09/2000</t>
-  </si>
-  <si>
     <t>יוני 2000 - יולי 2000</t>
   </si>
   <si>
-    <t>15/10/2000</t>
-  </si>
-  <si>
     <t>יולי 2000 - אוגוסט 2000</t>
   </si>
   <si>
-    <t>15/11/2000</t>
-  </si>
-  <si>
     <t>אוגוסט 2000 - ספטמבר 2000</t>
   </si>
   <si>
-    <t>15/12/2000</t>
-  </si>
-  <si>
     <t>ספטמבר 2000 - אוקטובר 2000</t>
   </si>
   <si>
-    <t>15/01/2001</t>
-  </si>
-  <si>
     <t>אוקטובר 2000 - נובמבר 2000</t>
   </si>
   <si>
-    <t>15/02/2001</t>
-  </si>
-  <si>
     <t>נובמבר 2000 - דצמבר 2000</t>
   </si>
   <si>
-    <t>15/03/2001</t>
-  </si>
-  <si>
     <t>דצמבר 2000 - ינואר 2001</t>
   </si>
   <si>
-    <t>15/04/2001</t>
-  </si>
-  <si>
     <t>ינואר 2001 - פברואר 2001</t>
   </si>
   <si>
-    <t>15/05/2001</t>
-  </si>
-  <si>
     <t>פברואר 2001 - מרס 2001</t>
   </si>
   <si>
-    <t>15/06/2001</t>
-  </si>
-  <si>
     <t>מרס 2001 - אפריל 2001</t>
   </si>
   <si>
-    <t>15/07/2001</t>
-  </si>
-  <si>
     <t>אפריל 2001 - מאי 2001</t>
   </si>
   <si>
-    <t>15/08/2001</t>
-  </si>
-  <si>
     <t>מאי 2001 - יוני 2001</t>
   </si>
   <si>
-    <t>15/09/2001</t>
-  </si>
-  <si>
     <t>יוני 2001 - יולי 2001</t>
   </si>
   <si>
-    <t>15/10/2001</t>
-  </si>
-  <si>
     <t>יולי 2001 - אוגוסט 2001</t>
   </si>
   <si>
-    <t>15/11/2001</t>
-  </si>
-  <si>
     <t>אוגוסט 2001 - ספטמבר 2001</t>
   </si>
   <si>
-    <t>15/12/2001</t>
-  </si>
-  <si>
     <t>ספטמבר 2001 - אוקטובר 2001</t>
   </si>
   <si>
-    <t>15/01/2002</t>
-  </si>
-  <si>
     <t>אוקטובר 2001 - נובמבר 2001</t>
   </si>
   <si>
-    <t>15/02/2002</t>
-  </si>
-  <si>
     <t>נובמבר 2001 - דצמבר 2001</t>
   </si>
   <si>
-    <t>15/03/2002</t>
-  </si>
-  <si>
     <t>דצמבר 2001 - ינואר 2002</t>
   </si>
   <si>
-    <t>15/04/2002</t>
-  </si>
-  <si>
     <t>ינואר 2002 - פברואר 2002</t>
   </si>
   <si>
-    <t>15/05/2002</t>
-  </si>
-  <si>
     <t>פברואר 2002 - מרס 2002</t>
   </si>
   <si>
-    <t>15/06/2002</t>
-  </si>
-  <si>
     <t>מרס 2002 - אפריל 2002</t>
   </si>
   <si>
-    <t>15/07/2002</t>
-  </si>
-  <si>
     <t>אפריל 2002 - מאי 2002</t>
   </si>
   <si>
-    <t>15/08/2002</t>
-  </si>
-  <si>
     <t>מאי 2002 - יוני 2002</t>
   </si>
   <si>
-    <t>15/09/2002</t>
-  </si>
-  <si>
     <t>יוני 2002 - יולי 2002</t>
   </si>
   <si>
-    <t>15/10/2002</t>
-  </si>
-  <si>
     <t>יולי 2002 - אוגוסט 2002</t>
   </si>
   <si>
-    <t>15/11/2002</t>
-  </si>
-  <si>
     <t>אוגוסט 2002 - ספטמבר 2002</t>
   </si>
   <si>
-    <t>15/12/2002</t>
-  </si>
-  <si>
     <t>ספטמבר 2002 - אוקטובר 2002</t>
   </si>
   <si>
-    <t>15/01/2003</t>
-  </si>
-  <si>
     <t>אוקטובר 2002 - נובמבר 2002</t>
   </si>
   <si>
-    <t>15/02/2003</t>
-  </si>
-  <si>
     <t>נובמבר 2002 - דצמבר 2002</t>
   </si>
   <si>
-    <t>15/03/2003</t>
-  </si>
-  <si>
     <t>דצמבר 2002 - ינואר 2003</t>
   </si>
   <si>
-    <t>15/04/2003</t>
-  </si>
-  <si>
     <t>ינואר 2003 - פברואר 2003</t>
   </si>
   <si>
-    <t>15/05/2003</t>
-  </si>
-  <si>
     <t>פברואר 2003 - מרס 2003</t>
   </si>
   <si>
-    <t>15/06/2003</t>
-  </si>
-  <si>
     <t>מרס 2003 - אפריל 2003</t>
   </si>
   <si>
-    <t>15/07/2003</t>
-  </si>
-  <si>
     <t>אפריל 2003 - מאי 2003</t>
   </si>
   <si>
-    <t>15/08/2003</t>
-  </si>
-  <si>
     <t>מאי 2003 - יוני 2003</t>
   </si>
   <si>
-    <t>15/09/2003</t>
-  </si>
-  <si>
     <t>יוני 2003 - יולי 2003</t>
   </si>
   <si>
-    <t>15/10/2003</t>
-  </si>
-  <si>
     <t>יולי 2003 - אוגוסט 2003</t>
   </si>
   <si>
-    <t>15/11/2003</t>
-  </si>
-  <si>
     <t>אוגוסט 2003 - ספטמבר 2003</t>
   </si>
   <si>
-    <t>15/12/2003</t>
-  </si>
-  <si>
     <t>ספטמבר 2003 - אוקטובר 2003</t>
   </si>
   <si>
-    <t>15/01/2004</t>
-  </si>
-  <si>
     <t>אוקטובר 2003 - נובמבר 2003</t>
   </si>
   <si>
-    <t>15/02/2004</t>
-  </si>
-  <si>
     <t>נובמבר 2003 - דצמבר 2003</t>
   </si>
   <si>
-    <t>15/03/2004</t>
-  </si>
-  <si>
     <t>דצמבר 2003 - ינואר 2004</t>
   </si>
   <si>
-    <t>15/04/2004</t>
-  </si>
-  <si>
     <t>ינואר 2004 - פברואר 2004</t>
   </si>
   <si>
-    <t>15/05/2004</t>
-  </si>
-  <si>
     <t>פברואר 2004 - מרס 2004</t>
   </si>
   <si>
-    <t>15/06/2004</t>
-  </si>
-  <si>
     <t>מרס 2004 - אפריל 2004</t>
   </si>
   <si>
-    <t>15/07/2004</t>
-  </si>
-  <si>
     <t>אפריל 2004 - מאי 2004</t>
   </si>
   <si>
-    <t>15/08/2004</t>
-  </si>
-  <si>
     <t>מאי 2004 - יוני 2004</t>
   </si>
   <si>
-    <t>15/09/2004</t>
-  </si>
-  <si>
     <t>יוני 2004 - יולי 2004</t>
   </si>
   <si>
-    <t>15/10/2004</t>
-  </si>
-  <si>
     <t>יולי 2004 - אוגוסט 2004</t>
   </si>
   <si>
-    <t>15/11/2004</t>
-  </si>
-  <si>
     <t>אוגוסט 2004 - ספטמבר 2004</t>
   </si>
   <si>
-    <t>15/12/2004</t>
-  </si>
-  <si>
     <t>ספטמבר 2004 - אוקטובר 2004</t>
   </si>
   <si>
-    <t>15/01/2005</t>
-  </si>
-  <si>
     <t>אוקטובר 2004 - נובמבר 2004</t>
   </si>
   <si>
-    <t>15/02/2005</t>
-  </si>
-  <si>
     <t>נובמבר 2004 - דצמבר 2004</t>
   </si>
   <si>
-    <t>15/03/2005</t>
-  </si>
-  <si>
     <t>דצמבר 2004 - ינואר 2005</t>
   </si>
   <si>
-    <t>15/04/2005</t>
-  </si>
-  <si>
     <t>ינואר 2005 - פברואר 2005</t>
   </si>
   <si>
-    <t>15/05/2005</t>
-  </si>
-  <si>
     <t>פברואר 2005 - מרס 2005</t>
   </si>
   <si>
-    <t>15/06/2005</t>
-  </si>
-  <si>
     <t>מרס 2005 - אפריל 2005</t>
   </si>
   <si>
-    <t>15/07/2005</t>
-  </si>
-  <si>
     <t>אפריל 2005 - מאי 2005</t>
   </si>
   <si>
-    <t>15/08/2005</t>
-  </si>
-  <si>
     <t>מאי 2005 - יוני 2005</t>
   </si>
   <si>
-    <t>15/09/2005</t>
-  </si>
-  <si>
     <t>יוני 2005 - יולי 2005</t>
   </si>
   <si>
-    <t>15/10/2005</t>
-  </si>
-  <si>
     <t>יולי 2005 - אוגוסט 2005</t>
   </si>
   <si>
-    <t>15/11/2005</t>
-  </si>
-  <si>
     <t>אוגוסט 2005 - ספטמבר 2005</t>
   </si>
   <si>
-    <t>15/12/2005</t>
-  </si>
-  <si>
     <t>ספטמבר 2005 - אוקטובר 2005</t>
   </si>
   <si>
-    <t>15/01/2006</t>
-  </si>
-  <si>
     <t>אוקטובר 2005 - נובמבר 2005</t>
   </si>
   <si>
-    <t>15/02/2006</t>
-  </si>
-  <si>
     <t>נובמבר 2005 - דצמבר 2005</t>
   </si>
   <si>
-    <t>15/03/2006</t>
-  </si>
-  <si>
     <t>דצמבר 2005 - ינואר 2006</t>
   </si>
   <si>
-    <t>15/04/2006</t>
-  </si>
-  <si>
     <t>ינואר 2006 - פברואר 2006</t>
   </si>
   <si>
-    <t>15/05/2006</t>
-  </si>
-  <si>
     <t>פברואר 2006 - מרס 2006</t>
   </si>
   <si>
-    <t>15/06/2006</t>
-  </si>
-  <si>
     <t>מרס 2006 - אפריל 2006</t>
   </si>
   <si>
-    <t>15/07/2006</t>
-  </si>
-  <si>
     <t>אפריל 2006 - מאי 2006</t>
   </si>
   <si>
-    <t>15/08/2006</t>
-  </si>
-  <si>
     <t>מאי 2006 - יוני 2006</t>
   </si>
   <si>
-    <t>15/09/2006</t>
-  </si>
-  <si>
     <t>יוני 2006 - יולי 2006</t>
   </si>
   <si>
-    <t>15/10/2006</t>
-  </si>
-  <si>
     <t>יולי 2006 - אוגוסט 2006</t>
   </si>
   <si>
-    <t>15/11/2006</t>
-  </si>
-  <si>
     <t>אוגוסט 2006 - ספטמבר 2006</t>
   </si>
   <si>
-    <t>15/12/2006</t>
-  </si>
-  <si>
     <t>ספטמבר 2006 - אוקטובר 2006</t>
   </si>
   <si>
-    <t>15/01/2007</t>
-  </si>
-  <si>
     <t>אוקטובר 2006 - נובמבר 2006</t>
   </si>
   <si>
-    <t>15/02/2007</t>
-  </si>
-  <si>
     <t>נובמבר 2006 - דצמבר 2006</t>
   </si>
   <si>
-    <t>15/03/2007</t>
-  </si>
-  <si>
     <t>דצמבר 2006 - ינואר 2007</t>
   </si>
   <si>
-    <t>15/04/2007</t>
-  </si>
-  <si>
     <t>ינואר 2007 - פברואר 2007</t>
   </si>
   <si>
-    <t>15/05/2007</t>
-  </si>
-  <si>
     <t>פברואר 2007 - מרס 2007</t>
   </si>
   <si>
-    <t>15/06/2007</t>
-  </si>
-  <si>
     <t>מרס 2007 - אפריל 2007</t>
   </si>
   <si>
-    <t>15/07/2007</t>
-  </si>
-  <si>
     <t>אפריל 2007 - מאי 2007</t>
   </si>
   <si>
-    <t>15/08/2007</t>
-  </si>
-  <si>
     <t>מאי 2007 - יוני 2007</t>
   </si>
   <si>
-    <t>15/09/2007</t>
-  </si>
-  <si>
     <t>יוני 2007 - יולי 2007</t>
   </si>
   <si>
-    <t>15/10/2007</t>
-  </si>
-  <si>
     <t>יולי 2007 - אוגוסט 2007</t>
   </si>
   <si>
-    <t>15/11/2007</t>
-  </si>
-  <si>
     <t>אוגוסט 2007 - ספטמבר 2007</t>
   </si>
   <si>
-    <t>15/12/2007</t>
-  </si>
-  <si>
     <t>ספטמבר 2007 - אוקטובר 2007</t>
   </si>
   <si>
-    <t>15/01/2008</t>
-  </si>
-  <si>
     <t>אוקטובר 2007 - נובמבר 2007</t>
   </si>
   <si>
-    <t>15/02/2008</t>
-  </si>
-  <si>
     <t>נובמבר 2007 - דצמבר 2007</t>
   </si>
   <si>
-    <t>15/03/2008</t>
-  </si>
-  <si>
     <t>דצמבר 2007 - ינואר 2008</t>
   </si>
   <si>
-    <t>15/04/2008</t>
-  </si>
-  <si>
     <t>ינואר 2008 - פברואר 2008</t>
   </si>
   <si>
-    <t>15/05/2008</t>
-  </si>
-  <si>
     <t>פברואר 2008 - מרס 2008</t>
   </si>
   <si>
-    <t>15/06/2008</t>
-  </si>
-  <si>
     <t>מרס 2008 - אפריל 2008</t>
   </si>
   <si>
-    <t>15/07/2008</t>
-  </si>
-  <si>
     <t>אפריל 2008 - מאי 2008</t>
   </si>
   <si>
-    <t>15/08/2008</t>
-  </si>
-  <si>
     <t>מאי 2008 - יוני 2008</t>
   </si>
   <si>
-    <t>15/09/2008</t>
-  </si>
-  <si>
     <t>יוני 2008 - יולי 2008</t>
   </si>
   <si>
-    <t>15/10/2008</t>
-  </si>
-  <si>
     <t>יולי 2008 - אוגוסט 2008</t>
   </si>
   <si>
-    <t>15/11/2008</t>
-  </si>
-  <si>
     <t>אוגוסט 2008 - ספטמבר 2008</t>
   </si>
   <si>
-    <t>15/12/2008</t>
-  </si>
-  <si>
     <t>ספטמבר 2008 - אוקטובר 2008</t>
   </si>
   <si>
-    <t>15/01/2009</t>
-  </si>
-  <si>
     <t>אוקטובר 2008 - נובמבר 2008</t>
   </si>
   <si>
-    <t>15/02/2009</t>
-  </si>
-  <si>
     <t>נובמבר 2008 - דצמבר 2008</t>
   </si>
   <si>
-    <t>15/03/2009</t>
-  </si>
-  <si>
     <t>דצמבר 2008 - ינואר 2009</t>
   </si>
   <si>
-    <t>15/04/2009</t>
-  </si>
-  <si>
     <t>ינואר 2009 - פברואר 2009</t>
   </si>
   <si>
-    <t>15/05/2009</t>
-  </si>
-  <si>
     <t>פברואר 2009 - מרס 2009</t>
   </si>
   <si>
-    <t>15/06/2009</t>
-  </si>
-  <si>
     <t>מרס 2009 - אפריל 2009</t>
   </si>
   <si>
-    <t>15/07/2009</t>
-  </si>
-  <si>
     <t>אפריל 2009 - מאי 2009</t>
   </si>
   <si>
-    <t>15/08/2009</t>
-  </si>
-  <si>
     <t>מאי 2009 - יוני 2009</t>
   </si>
   <si>
-    <t>15/09/2009</t>
-  </si>
-  <si>
     <t>יוני 2009 - יולי 2009</t>
   </si>
   <si>
-    <t>15/10/2009</t>
-  </si>
-  <si>
     <t>יולי 2009 - אוגוסט 2009</t>
   </si>
   <si>
-    <t>15/11/2009</t>
-  </si>
-  <si>
     <t>אוגוסט 2009 - ספטמבר 2009</t>
   </si>
   <si>
-    <t>15/12/2009</t>
-  </si>
-  <si>
     <t>ספטמבר 2009 - אוקטובר 2009</t>
   </si>
   <si>
-    <t>15/01/2010</t>
-  </si>
-  <si>
     <t>אוקטובר 2009 - נובמבר 2009</t>
   </si>
   <si>
-    <t>15/02/2010</t>
-  </si>
-  <si>
     <t>נובמבר 2009 - דצמבר 2009</t>
-  </si>
-  <si>
-    <t>15/03/2010</t>
   </si>
   <si>
     <t>דצמבר 2009 - ינואר 2010</t>
@@ -2544,20 +2562,20 @@
       <left/>
       <right/>
       <top style="double">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top style="double">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -2584,7 +2602,7 @@
     <xf numFmtId="189" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2605,9 +2623,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" readingOrder="2"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2617,7 +2632,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
   </cellXfs>
@@ -2911,31 +2929,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="15" t="s">
-        <v>408</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
+      <c r="A1" s="14" t="s">
+        <v>606</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
     </row>
     <row r="3" spans="1:5" ht="18.75">
-      <c r="A3" s="16" t="s">
-        <v>407</v>
-      </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
+      <c r="A3" s="15" t="s">
+        <v>413</v>
+      </c>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
     </row>
     <row r="5" spans="1:5" ht="24.75" thickTop="1">
       <c r="A5" s="1" t="s">
@@ -2966,10 +2984,10 @@
         <v>117.2</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>410</v>
+        <v>607</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2981,10 +2999,10 @@
         <v>119.6</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>412</v>
+        <v>608</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2996,10 +3014,10 @@
         <v>122.1</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>414</v>
+        <v>609</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -3011,10 +3029,10 @@
         <v>124.3</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>416</v>
+        <v>610</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -3026,10 +3044,10 @@
         <v>127.1</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>418</v>
+        <v>611</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -3044,7 +3062,7 @@
         <v>419</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>420</v>
+        <v>612</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -3056,10 +3074,10 @@
         <v>131.19999999999999</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>422</v>
+        <v>613</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -3071,10 +3089,10 @@
         <v>132.5</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>424</v>
+        <v>614</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -3086,10 +3104,10 @@
         <v>133.5</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>426</v>
+        <v>615</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -3101,10 +3119,10 @@
         <v>135.30000000000001</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>428</v>
+        <v>616</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -3116,10 +3134,10 @@
         <v>136.9</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>430</v>
+        <v>617</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -3131,10 +3149,10 @@
         <v>138.9</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>432</v>
+        <v>618</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -3148,10 +3166,10 @@
         <v>140.30000000000001</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>434</v>
+        <v>619</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -3165,10 +3183,10 @@
         <v>140.69999999999999</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>436</v>
+        <v>620</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -3182,10 +3200,10 @@
         <v>141.5</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>438</v>
+        <v>621</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -3199,10 +3217,10 @@
         <v>142.69999999999999</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>440</v>
+        <v>622</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -3216,10 +3234,10 @@
         <v>144.4</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>442</v>
+        <v>623</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -3233,10 +3251,10 @@
         <v>145.5</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>444</v>
+        <v>624</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -3250,10 +3268,10 @@
         <v>148.69999999999999</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>446</v>
+        <v>625</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -3267,10 +3285,10 @@
         <v>151.80000000000001</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>448</v>
+        <v>626</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -3284,10 +3302,10 @@
         <v>151.9</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>450</v>
+        <v>627</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -3301,10 +3319,10 @@
         <v>153.5</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>451</v>
+        <v>435</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>452</v>
+        <v>628</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -3318,10 +3336,10 @@
         <v>157.9</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>453</v>
+        <v>436</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>454</v>
+        <v>629</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -3335,10 +3353,10 @@
         <v>162.69999999999999</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>455</v>
+        <v>437</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>456</v>
+        <v>630</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -3352,10 +3370,10 @@
         <v>164.7</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>458</v>
+        <v>631</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -3369,10 +3387,10 @@
         <v>164.7</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>459</v>
+        <v>439</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>460</v>
+        <v>632</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -3386,10 +3404,10 @@
         <v>167</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>461</v>
+        <v>440</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>462</v>
+        <v>633</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -3403,10 +3421,10 @@
         <v>171.8</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>463</v>
+        <v>441</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>464</v>
+        <v>634</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -3420,10 +3438,10 @@
         <v>175.3</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>465</v>
+        <v>442</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>466</v>
+        <v>635</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -3437,10 +3455,10 @@
         <v>174.6</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>467</v>
+        <v>443</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>468</v>
+        <v>636</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -3454,10 +3472,10 @@
         <v>171.6</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>469</v>
+        <v>444</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>470</v>
+        <v>637</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -3471,10 +3489,10 @@
         <v>170.8</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>471</v>
+        <v>445</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>472</v>
+        <v>638</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -3488,10 +3506,10 @@
         <v>173.5</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>473</v>
+        <v>446</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>474</v>
+        <v>639</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -3505,10 +3523,10 @@
         <v>176.4</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>475</v>
+        <v>447</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>476</v>
+        <v>640</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -3522,10 +3540,10 @@
         <v>177.1</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>477</v>
+        <v>448</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>478</v>
+        <v>641</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -3539,10 +3557,10 @@
         <v>178.4</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>479</v>
+        <v>449</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>480</v>
+        <v>642</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -3556,10 +3574,10 @@
         <v>181.8</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>481</v>
+        <v>450</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>482</v>
+        <v>643</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -3573,10 +3591,10 @@
         <v>183</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>483</v>
+        <v>451</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>484</v>
+        <v>644</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -3590,10 +3608,10 @@
         <v>183.2</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>485</v>
+        <v>452</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>486</v>
+        <v>645</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -3607,10 +3625,10 @@
         <v>185.1</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>487</v>
+        <v>453</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>488</v>
+        <v>646</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -3624,10 +3642,10 @@
         <v>187.4</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>489</v>
+        <v>454</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>490</v>
+        <v>647</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -3641,10 +3659,10 @@
         <v>190.8</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>491</v>
+        <v>455</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>492</v>
+        <v>648</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -3658,10 +3676,10 @@
         <v>192.4</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>493</v>
+        <v>456</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>494</v>
+        <v>649</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -3675,10 +3693,10 @@
         <v>191.5</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>495</v>
+        <v>457</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>496</v>
+        <v>650</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -3692,10 +3710,10 @@
         <v>190.3</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>497</v>
+        <v>458</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>498</v>
+        <v>651</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -3709,10 +3727,10 @@
         <v>189.5</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>499</v>
+        <v>459</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>500</v>
+        <v>652</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -3726,10 +3744,10 @@
         <v>189.7</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>501</v>
+        <v>460</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>502</v>
+        <v>653</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -3743,10 +3761,10 @@
         <v>190.9</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>503</v>
+        <v>461</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>504</v>
+        <v>654</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -3760,10 +3778,10 @@
         <v>191.1</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>505</v>
+        <v>462</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>506</v>
+        <v>655</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -3777,10 +3795,10 @@
         <v>190.1</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>507</v>
+        <v>463</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>508</v>
+        <v>656</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -3794,10 +3812,10 @@
         <v>191.6</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>509</v>
+        <v>464</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>510</v>
+        <v>657</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -3811,10 +3829,10 @@
         <v>193.5</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>511</v>
+        <v>465</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>512</v>
+        <v>658</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -3828,10 +3846,10 @@
         <v>193.4</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>513</v>
+        <v>466</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>514</v>
+        <v>659</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -3845,10 +3863,10 @@
         <v>190.1</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>515</v>
+        <v>467</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>516</v>
+        <v>660</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -3862,10 +3880,10 @@
         <v>188.1</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>517</v>
+        <v>468</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>518</v>
+        <v>661</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -3879,10 +3897,10 @@
         <v>191</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>519</v>
+        <v>469</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>520</v>
+        <v>662</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -3896,10 +3914,10 @@
         <v>198.3</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>521</v>
+        <v>470</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>522</v>
+        <v>663</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -3913,10 +3931,10 @@
         <v>204.4</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>523</v>
+        <v>471</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>524</v>
+        <v>664</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -3930,10 +3948,10 @@
         <v>204.4</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>525</v>
+        <v>472</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>526</v>
+        <v>665</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -3947,10 +3965,10 @@
         <v>204.3</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>527</v>
+        <v>473</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>528</v>
+        <v>666</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -3964,10 +3982,10 @@
         <v>204.6</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>529</v>
+        <v>474</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>530</v>
+        <v>667</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -3981,10 +3999,10 @@
         <v>203.3</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>531</v>
+        <v>475</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>532</v>
+        <v>668</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -3998,10 +4016,10 @@
         <v>201.7</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>533</v>
+        <v>476</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>534</v>
+        <v>669</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -4015,10 +4033,10 @@
         <v>203</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>535</v>
+        <v>477</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>536</v>
+        <v>670</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -4032,10 +4050,10 @@
         <v>202.4</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>537</v>
+        <v>478</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>538</v>
+        <v>671</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -4049,10 +4067,10 @@
         <v>200.1</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>539</v>
+        <v>479</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>540</v>
+        <v>672</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -4066,10 +4084,10 @@
         <v>202.7</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>541</v>
+        <v>480</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>542</v>
+        <v>673</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -4083,10 +4101,10 @@
         <v>206.1</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>543</v>
+        <v>481</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>544</v>
+        <v>674</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -4100,10 +4118,10 @@
         <v>204</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>545</v>
+        <v>482</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>546</v>
+        <v>675</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -4117,10 +4135,10 @@
         <v>204.2</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>547</v>
+        <v>483</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>548</v>
+        <v>676</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -4134,10 +4152,10 @@
         <v>205.6</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>549</v>
+        <v>484</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>550</v>
+        <v>677</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -4151,10 +4169,10 @@
         <v>200.5</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>551</v>
+        <v>485</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>552</v>
+        <v>678</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -4168,10 +4186,10 @@
         <v>195.8</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>553</v>
+        <v>486</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>554</v>
+        <v>679</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -4185,10 +4203,10 @@
         <v>193.8</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>555</v>
+        <v>487</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>556</v>
+        <v>680</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -4202,10 +4220,10 @@
         <v>194.2</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>557</v>
+        <v>488</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>558</v>
+        <v>681</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -4219,10 +4237,10 @@
         <v>197.3</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>559</v>
+        <v>489</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>560</v>
+        <v>682</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -4236,10 +4254,10 @@
         <v>197.9</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>561</v>
+        <v>490</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>562</v>
+        <v>683</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -4253,10 +4271,10 @@
         <v>195.2</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>563</v>
+        <v>491</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>564</v>
+        <v>684</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -4270,10 +4288,10 @@
         <v>194.1</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>565</v>
+        <v>492</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>566</v>
+        <v>685</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -4287,10 +4305,10 @@
         <v>192.6</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>567</v>
+        <v>493</v>
       </c>
       <c r="E86" s="13" t="s">
-        <v>568</v>
+        <v>686</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -4304,10 +4322,10 @@
         <v>191.2</v>
       </c>
       <c r="D87" s="11" t="s">
-        <v>569</v>
+        <v>494</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>570</v>
+        <v>687</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -4321,10 +4339,10 @@
         <v>192.1</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>571</v>
+        <v>495</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>572</v>
+        <v>688</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -4338,10 +4356,10 @@
         <v>188.8</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>573</v>
+        <v>496</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>574</v>
+        <v>689</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -4355,10 +4373,10 @@
         <v>188</v>
       </c>
       <c r="D90" s="11" t="s">
-        <v>575</v>
+        <v>497</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>576</v>
+        <v>690</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -4372,10 +4390,10 @@
         <v>188.6</v>
       </c>
       <c r="D91" s="11" t="s">
-        <v>577</v>
+        <v>498</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>578</v>
+        <v>691</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -4389,10 +4407,10 @@
         <v>188.4</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>579</v>
+        <v>499</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>580</v>
+        <v>692</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -4406,10 +4424,10 @@
         <v>187.2</v>
       </c>
       <c r="D93" s="11" t="s">
-        <v>581</v>
+        <v>500</v>
       </c>
       <c r="E93" s="13" t="s">
-        <v>582</v>
+        <v>693</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -4423,10 +4441,10 @@
         <v>185.6</v>
       </c>
       <c r="D94" s="11" t="s">
-        <v>583</v>
+        <v>501</v>
       </c>
       <c r="E94" s="13" t="s">
-        <v>584</v>
+        <v>694</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -4440,10 +4458,10 @@
         <v>185.7</v>
       </c>
       <c r="D95" s="11" t="s">
-        <v>585</v>
+        <v>502</v>
       </c>
       <c r="E95" s="13" t="s">
-        <v>586</v>
+        <v>695</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -4457,10 +4475,10 @@
         <v>185.7</v>
       </c>
       <c r="D96" s="11" t="s">
-        <v>587</v>
+        <v>503</v>
       </c>
       <c r="E96" s="13" t="s">
-        <v>588</v>
+        <v>696</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -4474,10 +4492,10 @@
         <v>186</v>
       </c>
       <c r="D97" s="11" t="s">
-        <v>589</v>
+        <v>504</v>
       </c>
       <c r="E97" s="13" t="s">
-        <v>590</v>
+        <v>697</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -4491,10 +4509,10 @@
         <v>187.2</v>
       </c>
       <c r="D98" s="11" t="s">
-        <v>591</v>
+        <v>505</v>
       </c>
       <c r="E98" s="13" t="s">
-        <v>592</v>
+        <v>698</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -4508,10 +4526,10 @@
         <v>187.3</v>
       </c>
       <c r="D99" s="11" t="s">
-        <v>593</v>
+        <v>506</v>
       </c>
       <c r="E99" s="13" t="s">
-        <v>594</v>
+        <v>699</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -4525,10 +4543,10 @@
         <v>185.6</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>595</v>
+        <v>507</v>
       </c>
       <c r="E100" s="13" t="s">
-        <v>596</v>
+        <v>700</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -4542,10 +4560,10 @@
         <v>184.5</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>597</v>
+        <v>508</v>
       </c>
       <c r="E101" s="13" t="s">
-        <v>598</v>
+        <v>701</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -4559,10 +4577,10 @@
         <v>188.3</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>599</v>
+        <v>509</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>600</v>
+        <v>702</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -4576,10 +4594,10 @@
         <v>194.1</v>
       </c>
       <c r="D103" s="11" t="s">
-        <v>601</v>
+        <v>510</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>602</v>
+        <v>703</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -4593,10 +4611,10 @@
         <v>196.6</v>
       </c>
       <c r="D104" s="11" t="s">
-        <v>603</v>
+        <v>511</v>
       </c>
       <c r="E104" s="13" t="s">
-        <v>604</v>
+        <v>704</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -4610,10 +4628,10 @@
         <v>197.6</v>
       </c>
       <c r="D105" s="11" t="s">
-        <v>605</v>
+        <v>512</v>
       </c>
       <c r="E105" s="13" t="s">
-        <v>606</v>
+        <v>705</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -4627,10 +4645,10 @@
         <v>199.8</v>
       </c>
       <c r="D106" s="11" t="s">
-        <v>607</v>
+        <v>513</v>
       </c>
       <c r="E106" s="13" t="s">
-        <v>608</v>
+        <v>706</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -4644,10 +4662,10 @@
         <v>201.6</v>
       </c>
       <c r="D107" s="11" t="s">
-        <v>609</v>
+        <v>514</v>
       </c>
       <c r="E107" s="13" t="s">
-        <v>610</v>
+        <v>707</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -4661,10 +4679,10 @@
         <v>198.8</v>
       </c>
       <c r="D108" s="11" t="s">
-        <v>611</v>
+        <v>515</v>
       </c>
       <c r="E108" s="13" t="s">
-        <v>612</v>
+        <v>708</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -4678,10 +4696,10 @@
         <v>196.4</v>
       </c>
       <c r="D109" s="11" t="s">
-        <v>613</v>
+        <v>516</v>
       </c>
       <c r="E109" s="13" t="s">
-        <v>614</v>
+        <v>709</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -4695,10 +4713,10 @@
         <v>196.6</v>
       </c>
       <c r="D110" s="11" t="s">
-        <v>615</v>
+        <v>517</v>
       </c>
       <c r="E110" s="13" t="s">
-        <v>616</v>
+        <v>710</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -4712,10 +4730,10 @@
         <v>196.3</v>
       </c>
       <c r="D111" s="11" t="s">
-        <v>617</v>
+        <v>518</v>
       </c>
       <c r="E111" s="13" t="s">
-        <v>618</v>
+        <v>711</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -4729,10 +4747,10 @@
         <v>194.6</v>
       </c>
       <c r="D112" s="11" t="s">
-        <v>619</v>
+        <v>519</v>
       </c>
       <c r="E112" s="13" t="s">
-        <v>620</v>
+        <v>712</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -4746,10 +4764,10 @@
         <v>192.7</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>621</v>
+        <v>520</v>
       </c>
       <c r="E113" s="13" t="s">
-        <v>622</v>
+        <v>713</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -4763,10 +4781,10 @@
         <v>193</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>623</v>
+        <v>521</v>
       </c>
       <c r="E114" s="13" t="s">
-        <v>624</v>
+        <v>714</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -4780,10 +4798,10 @@
         <v>193.6</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>625</v>
+        <v>522</v>
       </c>
       <c r="E115" s="13" t="s">
-        <v>626</v>
+        <v>715</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -4797,10 +4815,10 @@
         <v>192.7</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>627</v>
+        <v>523</v>
       </c>
       <c r="E116" s="13" t="s">
-        <v>628</v>
+        <v>716</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -4814,10 +4832,10 @@
         <v>188.2</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>629</v>
+        <v>524</v>
       </c>
       <c r="E117" s="13" t="s">
-        <v>630</v>
+        <v>717</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -4831,10 +4849,10 @@
         <v>184.8</v>
       </c>
       <c r="D118" s="11" t="s">
-        <v>631</v>
+        <v>525</v>
       </c>
       <c r="E118" s="13" t="s">
-        <v>632</v>
+        <v>718</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -4848,10 +4866,10 @@
         <v>183.8</v>
       </c>
       <c r="D119" s="11" t="s">
-        <v>633</v>
+        <v>526</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>634</v>
+        <v>719</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -4865,10 +4883,10 @@
         <v>181.8</v>
       </c>
       <c r="D120" s="11" t="s">
-        <v>635</v>
+        <v>527</v>
       </c>
       <c r="E120" s="13" t="s">
-        <v>636</v>
+        <v>720</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -4882,10 +4900,10 @@
         <v>183.4</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>637</v>
+        <v>528</v>
       </c>
       <c r="E121" s="13" t="s">
-        <v>638</v>
+        <v>721</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -4899,10 +4917,10 @@
         <v>185.9</v>
       </c>
       <c r="D122" s="11" t="s">
-        <v>639</v>
+        <v>529</v>
       </c>
       <c r="E122" s="13" t="s">
-        <v>640</v>
+        <v>722</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -4916,10 +4934,10 @@
         <v>183.7</v>
       </c>
       <c r="D123" s="11" t="s">
-        <v>641</v>
+        <v>530</v>
       </c>
       <c r="E123" s="13" t="s">
-        <v>642</v>
+        <v>723</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -4933,10 +4951,10 @@
         <v>182.8</v>
       </c>
       <c r="D124" s="11" t="s">
-        <v>643</v>
+        <v>531</v>
       </c>
       <c r="E124" s="13" t="s">
-        <v>644</v>
+        <v>724</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -4950,10 +4968,10 @@
         <v>182.6</v>
       </c>
       <c r="D125" s="11" t="s">
-        <v>645</v>
+        <v>532</v>
       </c>
       <c r="E125" s="13" t="s">
-        <v>646</v>
+        <v>725</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -4967,10 +4985,10 @@
         <v>181.2</v>
       </c>
       <c r="D126" s="11" t="s">
-        <v>647</v>
+        <v>533</v>
       </c>
       <c r="E126" s="13" t="s">
-        <v>648</v>
+        <v>726</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -4984,10 +5002,10 @@
         <v>182</v>
       </c>
       <c r="D127" s="11" t="s">
-        <v>649</v>
+        <v>534</v>
       </c>
       <c r="E127" s="13" t="s">
-        <v>650</v>
+        <v>727</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -5001,10 +5019,10 @@
         <v>183.7</v>
       </c>
       <c r="D128" s="11" t="s">
-        <v>651</v>
+        <v>535</v>
       </c>
       <c r="E128" s="13" t="s">
-        <v>652</v>
+        <v>728</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -5018,10 +5036,10 @@
         <v>184.9</v>
       </c>
       <c r="D129" s="11" t="s">
-        <v>653</v>
+        <v>536</v>
       </c>
       <c r="E129" s="13" t="s">
-        <v>654</v>
+        <v>729</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -5035,10 +5053,10 @@
         <v>186.6</v>
       </c>
       <c r="D130" s="11" t="s">
-        <v>655</v>
+        <v>537</v>
       </c>
       <c r="E130" s="13" t="s">
-        <v>656</v>
+        <v>730</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -5052,10 +5070,10 @@
         <v>187.6</v>
       </c>
       <c r="D131" s="11" t="s">
-        <v>657</v>
+        <v>538</v>
       </c>
       <c r="E131" s="13" t="s">
-        <v>658</v>
+        <v>731</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -5069,10 +5087,10 @@
         <v>186.6</v>
       </c>
       <c r="D132" s="11" t="s">
-        <v>659</v>
+        <v>539</v>
       </c>
       <c r="E132" s="13" t="s">
-        <v>660</v>
+        <v>732</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -5086,10 +5104,10 @@
         <v>187.2</v>
       </c>
       <c r="D133" s="11" t="s">
-        <v>661</v>
+        <v>540</v>
       </c>
       <c r="E133" s="13" t="s">
-        <v>662</v>
+        <v>733</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -5103,10 +5121,10 @@
         <v>185.7</v>
       </c>
       <c r="D134" s="11" t="s">
-        <v>663</v>
+        <v>541</v>
       </c>
       <c r="E134" s="13" t="s">
-        <v>664</v>
+        <v>734</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -5120,10 +5138,10 @@
         <v>182.4</v>
       </c>
       <c r="D135" s="11" t="s">
-        <v>665</v>
+        <v>542</v>
       </c>
       <c r="E135" s="13" t="s">
-        <v>666</v>
+        <v>735</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -5137,10 +5155,10 @@
         <v>182</v>
       </c>
       <c r="D136" s="11" t="s">
-        <v>667</v>
+        <v>543</v>
       </c>
       <c r="E136" s="13" t="s">
-        <v>668</v>
+        <v>736</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -5154,10 +5172,10 @@
         <v>180.4</v>
       </c>
       <c r="D137" s="11" t="s">
-        <v>669</v>
+        <v>544</v>
       </c>
       <c r="E137" s="13" t="s">
-        <v>670</v>
+        <v>737</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -5171,10 +5189,10 @@
         <v>178.8</v>
       </c>
       <c r="D138" s="11" t="s">
-        <v>671</v>
+        <v>545</v>
       </c>
       <c r="E138" s="13" t="s">
-        <v>672</v>
+        <v>738</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -5188,10 +5206,10 @@
         <v>178.6</v>
       </c>
       <c r="D139" s="11" t="s">
-        <v>673</v>
+        <v>546</v>
       </c>
       <c r="E139" s="13" t="s">
-        <v>674</v>
+        <v>739</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -5205,10 +5223,10 @@
         <v>179.5</v>
       </c>
       <c r="D140" s="11" t="s">
-        <v>675</v>
+        <v>547</v>
       </c>
       <c r="E140" s="13" t="s">
-        <v>676</v>
+        <v>740</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -5222,10 +5240,10 @@
         <v>182.2</v>
       </c>
       <c r="D141" s="11" t="s">
-        <v>677</v>
+        <v>548</v>
       </c>
       <c r="E141" s="13" t="s">
-        <v>678</v>
+        <v>741</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -5239,10 +5257,10 @@
         <v>182.5</v>
       </c>
       <c r="D142" s="11" t="s">
-        <v>679</v>
+        <v>549</v>
       </c>
       <c r="E142" s="13" t="s">
-        <v>680</v>
+        <v>742</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -5256,10 +5274,10 @@
         <v>183.1</v>
       </c>
       <c r="D143" s="11" t="s">
-        <v>681</v>
+        <v>550</v>
       </c>
       <c r="E143" s="13" t="s">
-        <v>682</v>
+        <v>743</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -5273,10 +5291,10 @@
         <v>185.6</v>
       </c>
       <c r="D144" s="11" t="s">
-        <v>683</v>
+        <v>551</v>
       </c>
       <c r="E144" s="13" t="s">
-        <v>684</v>
+        <v>744</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -5290,10 +5308,10 @@
         <v>185.7</v>
       </c>
       <c r="D145" s="11" t="s">
-        <v>685</v>
+        <v>552</v>
       </c>
       <c r="E145" s="13" t="s">
-        <v>686</v>
+        <v>745</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -5307,10 +5325,10 @@
         <v>185.4</v>
       </c>
       <c r="D146" s="11" t="s">
-        <v>687</v>
+        <v>553</v>
       </c>
       <c r="E146" s="13" t="s">
-        <v>688</v>
+        <v>746</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -5324,10 +5342,10 @@
         <v>187.1</v>
       </c>
       <c r="D147" s="11" t="s">
-        <v>689</v>
+        <v>554</v>
       </c>
       <c r="E147" s="13" t="s">
-        <v>690</v>
+        <v>747</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -5341,10 +5359,10 @@
         <v>189</v>
       </c>
       <c r="D148" s="11" t="s">
-        <v>691</v>
+        <v>555</v>
       </c>
       <c r="E148" s="13" t="s">
-        <v>692</v>
+        <v>748</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -5358,10 +5376,10 @@
         <v>187.3</v>
       </c>
       <c r="D149" s="11" t="s">
-        <v>693</v>
+        <v>556</v>
       </c>
       <c r="E149" s="13" t="s">
-        <v>694</v>
+        <v>749</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -5375,10 +5393,10 @@
         <v>186.7</v>
       </c>
       <c r="D150" s="11" t="s">
-        <v>695</v>
+        <v>557</v>
       </c>
       <c r="E150" s="13" t="s">
-        <v>696</v>
+        <v>750</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -5392,10 +5410,10 @@
         <v>188.2</v>
       </c>
       <c r="D151" s="11" t="s">
-        <v>697</v>
+        <v>558</v>
       </c>
       <c r="E151" s="13" t="s">
-        <v>698</v>
+        <v>751</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -5409,10 +5427,10 @@
         <v>189.2</v>
       </c>
       <c r="D152" s="11" t="s">
-        <v>699</v>
+        <v>559</v>
       </c>
       <c r="E152" s="13" t="s">
-        <v>700</v>
+        <v>752</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -5426,10 +5444,10 @@
         <v>190.1</v>
       </c>
       <c r="D153" s="11" t="s">
-        <v>701</v>
+        <v>560</v>
       </c>
       <c r="E153" s="13" t="s">
-        <v>702</v>
+        <v>753</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -5443,10 +5461,10 @@
         <v>187.2</v>
       </c>
       <c r="D154" s="11" t="s">
-        <v>703</v>
+        <v>561</v>
       </c>
       <c r="E154" s="13" t="s">
-        <v>704</v>
+        <v>754</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -5460,10 +5478,10 @@
         <v>185.4</v>
       </c>
       <c r="D155" s="11" t="s">
-        <v>705</v>
+        <v>562</v>
       </c>
       <c r="E155" s="13" t="s">
-        <v>706</v>
+        <v>755</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -5477,10 +5495,10 @@
         <v>185.4</v>
       </c>
       <c r="D156" s="11" t="s">
-        <v>707</v>
+        <v>563</v>
       </c>
       <c r="E156" s="13" t="s">
-        <v>708</v>
+        <v>756</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -5494,10 +5512,10 @@
         <v>186.2</v>
       </c>
       <c r="D157" s="11" t="s">
-        <v>709</v>
+        <v>564</v>
       </c>
       <c r="E157" s="13" t="s">
-        <v>710</v>
+        <v>757</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -5511,10 +5529,10 @@
         <v>186.5</v>
       </c>
       <c r="D158" s="11" t="s">
-        <v>711</v>
+        <v>565</v>
       </c>
       <c r="E158" s="13" t="s">
-        <v>712</v>
+        <v>758</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -5528,10 +5546,10 @@
         <v>183.4</v>
       </c>
       <c r="D159" s="11" t="s">
-        <v>713</v>
+        <v>566</v>
       </c>
       <c r="E159" s="13" t="s">
-        <v>714</v>
+        <v>759</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -5545,10 +5563,10 @@
         <v>182.4</v>
       </c>
       <c r="D160" s="11" t="s">
-        <v>715</v>
+        <v>567</v>
       </c>
       <c r="E160" s="13" t="s">
-        <v>716</v>
+        <v>760</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -5562,10 +5580,10 @@
         <v>180.2</v>
       </c>
       <c r="D161" s="11" t="s">
-        <v>717</v>
+        <v>568</v>
       </c>
       <c r="E161" s="13" t="s">
-        <v>718</v>
+        <v>761</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -5579,10 +5597,10 @@
         <v>178.6</v>
       </c>
       <c r="D162" s="11" t="s">
-        <v>719</v>
+        <v>569</v>
       </c>
       <c r="E162" s="13" t="s">
-        <v>720</v>
+        <v>762</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -5596,10 +5614,10 @@
         <v>179.7</v>
       </c>
       <c r="D163" s="11" t="s">
-        <v>721</v>
+        <v>570</v>
       </c>
       <c r="E163" s="13" t="s">
-        <v>722</v>
+        <v>763</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -5613,10 +5631,10 @@
         <v>179.7</v>
       </c>
       <c r="D164" s="11" t="s">
-        <v>723</v>
+        <v>571</v>
       </c>
       <c r="E164" s="13" t="s">
-        <v>724</v>
+        <v>764</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -5630,10 +5648,10 @@
         <v>178.5</v>
       </c>
       <c r="D165" s="11" t="s">
-        <v>725</v>
+        <v>572</v>
       </c>
       <c r="E165" s="13" t="s">
-        <v>726</v>
+        <v>765</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -5647,10 +5665,10 @@
         <v>177.3</v>
       </c>
       <c r="D166" s="11" t="s">
-        <v>727</v>
+        <v>573</v>
       </c>
       <c r="E166" s="13" t="s">
-        <v>728</v>
+        <v>766</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -5664,10 +5682,10 @@
         <v>180.1</v>
       </c>
       <c r="D167" s="11" t="s">
-        <v>729</v>
+        <v>574</v>
       </c>
       <c r="E167" s="13" t="s">
-        <v>730</v>
+        <v>767</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -5681,10 +5699,10 @@
         <v>184.5</v>
       </c>
       <c r="D168" s="11" t="s">
-        <v>731</v>
+        <v>575</v>
       </c>
       <c r="E168" s="13" t="s">
-        <v>732</v>
+        <v>768</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -5698,10 +5716,10 @@
         <v>187.4</v>
       </c>
       <c r="D169" s="11" t="s">
-        <v>733</v>
+        <v>576</v>
       </c>
       <c r="E169" s="13" t="s">
-        <v>734</v>
+        <v>769</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -5715,10 +5733,10 @@
         <v>186.3</v>
       </c>
       <c r="D170" s="11" t="s">
-        <v>735</v>
+        <v>577</v>
       </c>
       <c r="E170" s="13" t="s">
-        <v>736</v>
+        <v>770</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -5732,10 +5750,10 @@
         <v>184.1</v>
       </c>
       <c r="D171" s="11" t="s">
-        <v>737</v>
+        <v>578</v>
       </c>
       <c r="E171" s="13" t="s">
-        <v>738</v>
+        <v>771</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -5749,10 +5767,10 @@
         <v>183.1</v>
       </c>
       <c r="D172" s="11" t="s">
-        <v>739</v>
+        <v>579</v>
       </c>
       <c r="E172" s="13" t="s">
-        <v>740</v>
+        <v>772</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -5766,10 +5784,10 @@
         <v>183.3</v>
       </c>
       <c r="D173" s="11" t="s">
-        <v>741</v>
+        <v>580</v>
       </c>
       <c r="E173" s="13" t="s">
-        <v>742</v>
+        <v>773</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -5783,10 +5801,10 @@
         <v>184.3</v>
       </c>
       <c r="D174" s="11" t="s">
-        <v>743</v>
+        <v>581</v>
       </c>
       <c r="E174" s="13" t="s">
-        <v>744</v>
+        <v>774</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -5800,10 +5818,10 @@
         <v>185.3</v>
       </c>
       <c r="D175" s="11" t="s">
-        <v>745</v>
+        <v>582</v>
       </c>
       <c r="E175" s="13" t="s">
-        <v>746</v>
+        <v>775</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -5817,10 +5835,10 @@
         <v>187.6</v>
       </c>
       <c r="D176" s="11" t="s">
-        <v>747</v>
+        <v>583</v>
       </c>
       <c r="E176" s="13" t="s">
-        <v>748</v>
+        <v>776</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -5834,10 +5852,10 @@
         <v>189.6</v>
       </c>
       <c r="D177" s="11" t="s">
-        <v>749</v>
+        <v>584</v>
       </c>
       <c r="E177" s="13" t="s">
-        <v>750</v>
+        <v>777</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -5851,10 +5869,10 @@
         <v>190</v>
       </c>
       <c r="D178" s="11" t="s">
-        <v>751</v>
+        <v>585</v>
       </c>
       <c r="E178" s="13" t="s">
-        <v>752</v>
+        <v>778</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -5868,10 +5886,10 @@
         <v>191.4</v>
       </c>
       <c r="D179" s="11" t="s">
-        <v>753</v>
+        <v>586</v>
       </c>
       <c r="E179" s="13" t="s">
-        <v>754</v>
+        <v>779</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -5885,10 +5903,10 @@
         <v>195.5</v>
       </c>
       <c r="D180" s="11" t="s">
-        <v>755</v>
+        <v>587</v>
       </c>
       <c r="E180" s="13" t="s">
-        <v>756</v>
+        <v>780</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -5902,10 +5920,10 @@
         <v>199.3</v>
       </c>
       <c r="D181" s="11" t="s">
-        <v>757</v>
+        <v>588</v>
       </c>
       <c r="E181" s="13" t="s">
-        <v>758</v>
+        <v>781</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -5919,10 +5937,10 @@
         <v>201.7</v>
       </c>
       <c r="D182" s="11" t="s">
-        <v>759</v>
+        <v>589</v>
       </c>
       <c r="E182" s="13" t="s">
-        <v>760</v>
+        <v>782</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -5936,10 +5954,10 @@
         <v>203.6</v>
       </c>
       <c r="D183" s="11" t="s">
-        <v>761</v>
+        <v>590</v>
       </c>
       <c r="E183" s="13" t="s">
-        <v>762</v>
+        <v>783</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -5953,10 +5971,10 @@
         <v>203.4</v>
       </c>
       <c r="D184" s="11" t="s">
-        <v>763</v>
+        <v>591</v>
       </c>
       <c r="E184" s="13" t="s">
-        <v>764</v>
+        <v>784</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -5970,10 +5988,10 @@
         <v>202.8</v>
       </c>
       <c r="D185" s="11" t="s">
-        <v>765</v>
+        <v>592</v>
       </c>
       <c r="E185" s="13" t="s">
-        <v>766</v>
+        <v>785</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -5987,10 +6005,10 @@
         <v>203.8</v>
       </c>
       <c r="D186" s="11" t="s">
-        <v>767</v>
+        <v>593</v>
       </c>
       <c r="E186" s="13" t="s">
-        <v>768</v>
+        <v>786</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -6004,10 +6022,10 @@
         <v>204.3</v>
       </c>
       <c r="D187" s="11" t="s">
-        <v>769</v>
+        <v>594</v>
       </c>
       <c r="E187" s="13" t="s">
-        <v>770</v>
+        <v>787</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -6021,10 +6039,10 @@
         <v>207.1</v>
       </c>
       <c r="D188" s="11" t="s">
-        <v>771</v>
+        <v>595</v>
       </c>
       <c r="E188" s="13" t="s">
-        <v>772</v>
+        <v>788</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -6038,10 +6056,10 @@
         <v>209.9</v>
       </c>
       <c r="D189" s="11" t="s">
-        <v>773</v>
+        <v>596</v>
       </c>
       <c r="E189" s="13" t="s">
-        <v>774</v>
+        <v>789</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -6055,10 +6073,10 @@
         <v>212.5</v>
       </c>
       <c r="D190" s="11" t="s">
-        <v>775</v>
+        <v>597</v>
       </c>
       <c r="E190" s="13" t="s">
-        <v>776</v>
+        <v>790</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -6072,10 +6090,10 @@
         <v>215.5</v>
       </c>
       <c r="D191" s="11" t="s">
-        <v>777</v>
+        <v>598</v>
       </c>
       <c r="E191" s="13" t="s">
-        <v>778</v>
+        <v>791</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -6089,10 +6107,10 @@
         <v>220.6</v>
       </c>
       <c r="D192" s="11" t="s">
-        <v>779</v>
+        <v>599</v>
       </c>
       <c r="E192" s="13" t="s">
-        <v>780</v>
+        <v>792</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -6106,10 +6124,10 @@
         <v>225.3</v>
       </c>
       <c r="D193" s="11" t="s">
-        <v>781</v>
+        <v>600</v>
       </c>
       <c r="E193" s="13" t="s">
-        <v>782</v>
+        <v>793</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -6123,10 +6141,10 @@
         <v>228.1</v>
       </c>
       <c r="D194" s="11" t="s">
-        <v>783</v>
+        <v>601</v>
       </c>
       <c r="E194" s="13" t="s">
-        <v>784</v>
+        <v>794</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -6140,10 +6158,10 @@
         <v>231.9</v>
       </c>
       <c r="D195" s="11" t="s">
-        <v>785</v>
+        <v>602</v>
       </c>
       <c r="E195" s="13" t="s">
-        <v>786</v>
+        <v>795</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -6157,10 +6175,10 @@
         <v>237.1</v>
       </c>
       <c r="D196" s="11" t="s">
-        <v>787</v>
+        <v>603</v>
       </c>
       <c r="E196" s="13" t="s">
-        <v>788</v>
+        <v>796</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -6174,10 +6192,10 @@
         <v>239.7</v>
       </c>
       <c r="D197" s="11" t="s">
-        <v>789</v>
+        <v>604</v>
       </c>
       <c r="E197" s="13" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -6191,10 +6209,10 @@
         <v>244.3</v>
       </c>
       <c r="D198" s="11" t="s">
-        <v>791</v>
+        <v>605</v>
       </c>
       <c r="E198" s="13" t="s">
-        <v>792</v>
+        <v>798</v>
       </c>
     </row>
     <row r="199" spans="1:5" ht="13.5" thickBot="1">
@@ -6208,103 +6226,103 @@
       <c r="E200" s="8"/>
     </row>
     <row r="201" spans="1:5">
-      <c r="A201" s="14" t="s">
-        <v>395</v>
-      </c>
-      <c r="B201" s="14"/>
-      <c r="C201" s="14"/>
-      <c r="D201" s="14"/>
-      <c r="E201" s="14"/>
+      <c r="A201" s="17" t="s">
+        <v>401</v>
+      </c>
+      <c r="B201" s="17"/>
+      <c r="C201" s="17"/>
+      <c r="D201" s="17"/>
+      <c r="E201" s="17"/>
     </row>
     <row r="202" spans="1:5">
-      <c r="A202" s="14" t="s">
-        <v>396</v>
-      </c>
-      <c r="B202" s="14"/>
-      <c r="C202" s="14"/>
-      <c r="D202" s="14"/>
-      <c r="E202" s="14"/>
+      <c r="A202" s="17" t="s">
+        <v>402</v>
+      </c>
+      <c r="B202" s="17"/>
+      <c r="C202" s="17"/>
+      <c r="D202" s="17"/>
+      <c r="E202" s="17"/>
     </row>
     <row r="203" spans="1:5">
-      <c r="A203" s="14" t="s">
-        <v>397</v>
-      </c>
-      <c r="B203" s="14"/>
-      <c r="C203" s="14"/>
-      <c r="D203" s="14"/>
-      <c r="E203" s="14"/>
+      <c r="A203" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B203" s="17"/>
+      <c r="C203" s="17"/>
+      <c r="D203" s="17"/>
+      <c r="E203" s="17"/>
     </row>
     <row r="204" spans="1:5">
-      <c r="A204" s="14" t="s">
-        <v>793</v>
-      </c>
-      <c r="B204" s="14"/>
-      <c r="C204" s="14"/>
-      <c r="D204" s="14"/>
-      <c r="E204" s="14"/>
+      <c r="A204" s="17" t="s">
+        <v>799</v>
+      </c>
+      <c r="B204" s="17"/>
+      <c r="C204" s="17"/>
+      <c r="D204" s="17"/>
+      <c r="E204" s="17"/>
     </row>
     <row r="205" spans="1:5">
-      <c r="A205" s="14" t="s">
-        <v>399</v>
-      </c>
-      <c r="B205" s="14"/>
-      <c r="C205" s="14"/>
-      <c r="D205" s="14"/>
-      <c r="E205" s="14"/>
+      <c r="A205" s="17" t="s">
+        <v>405</v>
+      </c>
+      <c r="B205" s="17"/>
+      <c r="C205" s="17"/>
+      <c r="D205" s="17"/>
+      <c r="E205" s="17"/>
     </row>
     <row r="206" spans="1:5">
-      <c r="A206" s="14" t="s">
-        <v>400</v>
-      </c>
-      <c r="B206" s="14"/>
-      <c r="C206" s="14"/>
-      <c r="D206" s="14"/>
-      <c r="E206" s="14"/>
+      <c r="A206" s="17" t="s">
+        <v>406</v>
+      </c>
+      <c r="B206" s="17"/>
+      <c r="C206" s="17"/>
+      <c r="D206" s="17"/>
+      <c r="E206" s="17"/>
     </row>
     <row r="207" spans="1:5">
-      <c r="A207" s="14" t="s">
-        <v>401</v>
-      </c>
-      <c r="B207" s="14"/>
-      <c r="C207" s="14"/>
-      <c r="D207" s="14"/>
-      <c r="E207" s="14"/>
+      <c r="A207" s="17" t="s">
+        <v>407</v>
+      </c>
+      <c r="B207" s="17"/>
+      <c r="C207" s="17"/>
+      <c r="D207" s="17"/>
+      <c r="E207" s="17"/>
     </row>
     <row r="208" spans="1:5">
-      <c r="A208" s="14" t="s">
-        <v>402</v>
-      </c>
-      <c r="B208" s="14"/>
-      <c r="C208" s="14"/>
-      <c r="D208" s="14"/>
-      <c r="E208" s="14"/>
+      <c r="A208" s="17" t="s">
+        <v>408</v>
+      </c>
+      <c r="B208" s="17"/>
+      <c r="C208" s="17"/>
+      <c r="D208" s="17"/>
+      <c r="E208" s="17"/>
     </row>
     <row r="209" spans="1:5">
-      <c r="A209" s="14" t="s">
-        <v>403</v>
-      </c>
-      <c r="B209" s="14"/>
-      <c r="C209" s="14"/>
-      <c r="D209" s="14"/>
-      <c r="E209" s="14"/>
+      <c r="A209" s="17" t="s">
+        <v>409</v>
+      </c>
+      <c r="B209" s="17"/>
+      <c r="C209" s="17"/>
+      <c r="D209" s="17"/>
+      <c r="E209" s="17"/>
     </row>
     <row r="210" spans="1:5">
-      <c r="A210" s="14" t="s">
-        <v>404</v>
-      </c>
-      <c r="B210" s="14"/>
-      <c r="C210" s="14"/>
-      <c r="D210" s="14"/>
-      <c r="E210" s="14"/>
+      <c r="A210" s="17" t="s">
+        <v>410</v>
+      </c>
+      <c r="B210" s="17"/>
+      <c r="C210" s="17"/>
+      <c r="D210" s="17"/>
+      <c r="E210" s="17"/>
     </row>
     <row r="211" spans="1:5">
-      <c r="A211" s="14" t="s">
-        <v>405</v>
-      </c>
-      <c r="B211" s="14"/>
-      <c r="C211" s="14"/>
-      <c r="D211" s="14"/>
-      <c r="E211" s="14"/>
+      <c r="A211" s="17" t="s">
+        <v>411</v>
+      </c>
+      <c r="B211" s="17"/>
+      <c r="C211" s="17"/>
+      <c r="D211" s="17"/>
+      <c r="E211" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -6331,7 +6349,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E214"/>
+  <dimension ref="A1:E217"/>
   <sheetFormatPr defaultColWidth="4.5703125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="13.7109375" style="4" customWidth="1"/>
@@ -6342,31 +6360,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
     </row>
     <row r="3" spans="1:5" ht="18.75">
-      <c r="A3" s="16" t="s">
-        <v>407</v>
-      </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
+      <c r="A3" s="15" t="s">
+        <v>413</v>
+      </c>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
     </row>
     <row r="4" spans="1:5" ht="15">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
     </row>
     <row r="5" spans="1:5" ht="24">
       <c r="A5" s="1" t="s">
@@ -9636,13 +9654,13 @@
       </c>
     </row>
     <row r="198" spans="1:5">
-      <c r="A198" s="6">
+      <c r="A198" s="5">
         <v>-1</v>
       </c>
-      <c r="B198" s="6">
+      <c r="B198" s="5">
         <v>-0.1</v>
       </c>
-      <c r="C198" s="10">
+      <c r="C198" s="9">
         <v>600.20000000000005</v>
       </c>
       <c r="D198" s="11" t="s">
@@ -9653,13 +9671,13 @@
       </c>
     </row>
     <row r="199" spans="1:5">
-      <c r="A199" s="6">
+      <c r="A199" s="5">
         <v>-1.7</v>
       </c>
-      <c r="B199" s="6">
+      <c r="B199" s="5">
         <v>-0.1</v>
       </c>
-      <c r="C199" s="10">
+      <c r="C199" s="9">
         <v>599.6</v>
       </c>
       <c r="D199" s="11" t="s">
@@ -9670,14 +9688,14 @@
       </c>
     </row>
     <row r="200" spans="1:5">
-      <c r="A200" s="6">
-        <v>-1.2</v>
-      </c>
-      <c r="B200" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="C200" s="10">
-        <v>601.4</v>
+      <c r="A200" s="5">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="B200" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="C200" s="9">
+        <v>602</v>
       </c>
       <c r="D200" s="11" t="s">
         <v>394</v>
@@ -9687,140 +9705,191 @@
       </c>
     </row>
     <row r="201" spans="1:5">
-      <c r="E201" s="12"/>
+      <c r="A201" s="6">
+        <v>-1.3</v>
+      </c>
+      <c r="B201" s="6">
+        <v>-0.4</v>
+      </c>
+      <c r="C201" s="10">
+        <v>599.6</v>
+      </c>
+      <c r="D201" s="11" t="s">
+        <v>396</v>
+      </c>
+      <c r="E201" s="13" t="s">
+        <v>395</v>
+      </c>
     </row>
     <row r="202" spans="1:5">
-      <c r="A202" s="7"/>
-      <c r="B202" s="8"/>
-      <c r="C202" s="8"/>
-      <c r="D202" s="8"/>
-      <c r="E202" s="8"/>
+      <c r="A202" s="6">
+        <v>-2</v>
+      </c>
+      <c r="B202" s="6">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="C202" s="10">
+        <v>593</v>
+      </c>
+      <c r="D202" s="11" t="s">
+        <v>398</v>
+      </c>
+      <c r="E202" s="13" t="s">
+        <v>397</v>
+      </c>
     </row>
     <row r="203" spans="1:5">
-      <c r="A203" s="14" t="s">
-        <v>395</v>
-      </c>
-      <c r="B203" s="14"/>
-      <c r="C203" s="14"/>
-      <c r="D203" s="14"/>
-      <c r="E203" s="14"/>
+      <c r="A203" s="6">
+        <v>-1.5</v>
+      </c>
+      <c r="B203" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="C203" s="10">
+        <v>593.6</v>
+      </c>
+      <c r="D203" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="E203" s="13" t="s">
+        <v>399</v>
+      </c>
     </row>
     <row r="204" spans="1:5">
-      <c r="A204" s="14" t="s">
-        <v>396</v>
-      </c>
-      <c r="B204" s="14"/>
-      <c r="C204" s="14"/>
-      <c r="D204" s="14"/>
-      <c r="E204" s="14"/>
+      <c r="E204" s="12"/>
     </row>
     <row r="205" spans="1:5">
-      <c r="A205" s="14" t="s">
-        <v>397</v>
-      </c>
-      <c r="B205" s="14"/>
-      <c r="C205" s="14"/>
-      <c r="D205" s="14"/>
-      <c r="E205" s="14"/>
+      <c r="A205" s="7"/>
+      <c r="B205" s="8"/>
+      <c r="C205" s="8"/>
+      <c r="D205" s="8"/>
+      <c r="E205" s="8"/>
     </row>
     <row r="206" spans="1:5">
-      <c r="A206" s="14" t="s">
-        <v>398</v>
-      </c>
-      <c r="B206" s="14"/>
-      <c r="C206" s="14"/>
-      <c r="D206" s="14"/>
-      <c r="E206" s="14"/>
+      <c r="A206" s="17" t="s">
+        <v>401</v>
+      </c>
+      <c r="B206" s="17"/>
+      <c r="C206" s="17"/>
+      <c r="D206" s="17"/>
+      <c r="E206" s="17"/>
     </row>
     <row r="207" spans="1:5">
-      <c r="A207" s="14" t="s">
-        <v>399</v>
-      </c>
-      <c r="B207" s="14"/>
-      <c r="C207" s="14"/>
-      <c r="D207" s="14"/>
-      <c r="E207" s="14"/>
+      <c r="A207" s="17" t="s">
+        <v>402</v>
+      </c>
+      <c r="B207" s="17"/>
+      <c r="C207" s="17"/>
+      <c r="D207" s="17"/>
+      <c r="E207" s="17"/>
     </row>
     <row r="208" spans="1:5">
-      <c r="A208" s="14" t="s">
-        <v>400</v>
-      </c>
-      <c r="B208" s="14"/>
-      <c r="C208" s="14"/>
-      <c r="D208" s="14"/>
-      <c r="E208" s="14"/>
+      <c r="A208" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="B208" s="17"/>
+      <c r="C208" s="17"/>
+      <c r="D208" s="17"/>
+      <c r="E208" s="17"/>
     </row>
     <row r="209" spans="1:5">
-      <c r="A209" s="14" t="s">
-        <v>401</v>
-      </c>
-      <c r="B209" s="14"/>
-      <c r="C209" s="14"/>
-      <c r="D209" s="14"/>
-      <c r="E209" s="14"/>
+      <c r="A209" s="17" t="s">
+        <v>404</v>
+      </c>
+      <c r="B209" s="17"/>
+      <c r="C209" s="17"/>
+      <c r="D209" s="17"/>
+      <c r="E209" s="17"/>
     </row>
     <row r="210" spans="1:5">
-      <c r="A210" s="14" t="s">
-        <v>402</v>
-      </c>
-      <c r="B210" s="14"/>
-      <c r="C210" s="14"/>
-      <c r="D210" s="14"/>
-      <c r="E210" s="14"/>
+      <c r="A210" s="17" t="s">
+        <v>405</v>
+      </c>
+      <c r="B210" s="17"/>
+      <c r="C210" s="17"/>
+      <c r="D210" s="17"/>
+      <c r="E210" s="17"/>
     </row>
     <row r="211" spans="1:5">
-      <c r="A211" s="14" t="s">
-        <v>403</v>
-      </c>
-      <c r="B211" s="14"/>
-      <c r="C211" s="14"/>
-      <c r="D211" s="14"/>
-      <c r="E211" s="14"/>
+      <c r="A211" s="17" t="s">
+        <v>406</v>
+      </c>
+      <c r="B211" s="17"/>
+      <c r="C211" s="17"/>
+      <c r="D211" s="17"/>
+      <c r="E211" s="17"/>
     </row>
     <row r="212" spans="1:5">
-      <c r="A212" s="14" t="s">
-        <v>404</v>
-      </c>
-      <c r="B212" s="14"/>
-      <c r="C212" s="14"/>
-      <c r="D212" s="14"/>
-      <c r="E212" s="14"/>
+      <c r="A212" s="17" t="s">
+        <v>407</v>
+      </c>
+      <c r="B212" s="17"/>
+      <c r="C212" s="17"/>
+      <c r="D212" s="17"/>
+      <c r="E212" s="17"/>
     </row>
     <row r="213" spans="1:5">
-      <c r="A213" s="14" t="s">
-        <v>405</v>
-      </c>
-      <c r="B213" s="14"/>
-      <c r="C213" s="14"/>
-      <c r="D213" s="14"/>
-      <c r="E213" s="14"/>
+      <c r="A213" s="17" t="s">
+        <v>408</v>
+      </c>
+      <c r="B213" s="17"/>
+      <c r="C213" s="17"/>
+      <c r="D213" s="17"/>
+      <c r="E213" s="17"/>
     </row>
     <row r="214" spans="1:5">
-      <c r="A214" s="14" t="s">
-        <v>406</v>
-      </c>
-      <c r="B214" s="14"/>
-      <c r="C214" s="14"/>
-      <c r="D214" s="14"/>
-      <c r="E214" s="14"/>
+      <c r="A214" s="17" t="s">
+        <v>409</v>
+      </c>
+      <c r="B214" s="17"/>
+      <c r="C214" s="17"/>
+      <c r="D214" s="17"/>
+      <c r="E214" s="17"/>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" s="17" t="s">
+        <v>410</v>
+      </c>
+      <c r="B215" s="17"/>
+      <c r="C215" s="17"/>
+      <c r="D215" s="17"/>
+      <c r="E215" s="17"/>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" s="17" t="s">
+        <v>411</v>
+      </c>
+      <c r="B216" s="17"/>
+      <c r="C216" s="17"/>
+      <c r="D216" s="17"/>
+      <c r="E216" s="17"/>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" s="17" t="s">
+        <v>412</v>
+      </c>
+      <c r="B217" s="17"/>
+      <c r="C217" s="17"/>
+      <c r="D217" s="17"/>
+      <c r="E217" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A214:E214"/>
+    <mergeCell ref="A215:E215"/>
+    <mergeCell ref="A216:E216"/>
+    <mergeCell ref="A217:E217"/>
+    <mergeCell ref="A208:E208"/>
+    <mergeCell ref="A209:E209"/>
+    <mergeCell ref="A210:E210"/>
+    <mergeCell ref="A211:E211"/>
+    <mergeCell ref="A212:E212"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A203:E203"/>
-    <mergeCell ref="A204:E204"/>
-    <mergeCell ref="A210:E210"/>
-    <mergeCell ref="A211:E211"/>
-    <mergeCell ref="A212:E212"/>
-    <mergeCell ref="A213:E213"/>
-    <mergeCell ref="A214:E214"/>
-    <mergeCell ref="A205:E205"/>
     <mergeCell ref="A206:E206"/>
     <mergeCell ref="A207:E207"/>
-    <mergeCell ref="A208:E208"/>
-    <mergeCell ref="A209:E209"/>
+    <mergeCell ref="A213:E213"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.5"/>
